--- a/九龙-启德-The Henley I/The Henley I_销控明细表.xlsx
+++ b/九龙-启德-The Henley I/The Henley I_销控明细表.xlsx
@@ -15053,7 +15053,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -32586,7 +32586,7 @@
           <t>A | 890呎 (3房)
 $2831万
 $31,810/呎
-(26年-08月-18日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
       <c r="C30" s="23" t="inlineStr">

--- a/九龙-启德-The Henley I/The Henley I_销控明细表.xlsx
+++ b/九龙-启德-The Henley I/The Henley I_销控明细表.xlsx
@@ -15606,34 +15606,34 @@
       </c>
       <c r="F242" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
-        <v>2796300028662000</v>
+        <v>27658800</v>
       </c>
       <c r="I242" s="5" t="n">
-        <v>3145444351701</v>
+        <v>31112</v>
       </c>
       <c r="J242" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K242" s="5" t="n">
-        <v>2583746272733300</v>
+        <v>27658800</v>
       </c>
       <c r="L242" s="5" t="n">
-        <v>2906351262917</v>
+        <v>31112</v>
       </c>
       <c r="M242" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N242" s="3" t="inlineStr">
@@ -16164,34 +16164,34 @@
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
-        <v>2796000028659000</v>
+        <v>27655900</v>
       </c>
       <c r="I251" s="5" t="n">
-        <v>3145106893880</v>
+        <v>31109</v>
       </c>
       <c r="J251" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K251" s="5" t="n">
-        <v>2583469076480500</v>
+        <v>27655900</v>
       </c>
       <c r="L251" s="5" t="n">
-        <v>2906039456109</v>
+        <v>31109</v>
       </c>
       <c r="M251" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N251" s="3" t="inlineStr">
@@ -30238,38 +30238,30 @@
       </c>
       <c r="F478" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G478" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H478" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I478" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H478" s="5" t="n">
+        <v>5888000</v>
+      </c>
+      <c r="I478" s="5" t="n">
+        <v>31656</v>
       </c>
       <c r="J478" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K478" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L478" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K478" s="5" t="n">
+        <v>5888000</v>
+      </c>
+      <c r="L478" s="5" t="n">
+        <v>31656</v>
       </c>
       <c r="M478" s="3" t="inlineStr">
         <is>
@@ -30278,7 +30270,7 @@
       </c>
       <c r="N478" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -30545,7 +30537,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -30555,7 +30547,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>225</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -32660,12 +32652,12 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B31" s="22" t="inlineStr">
+      <c r="B31" s="20" t="inlineStr">
         <is>
           <t>A | 889呎 (3房)
-$279630002866万
-$3,145,444,351,701/呎
-(在售)</t>
+$2766万
+$31,112/呎
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="C31" s="22" t="inlineStr">
@@ -32739,12 +32731,12 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B32" s="22" t="inlineStr">
+      <c r="B32" s="20" t="inlineStr">
         <is>
           <t>A | 889呎 (3房)
-$279600002866万
-$3,145,106,893,880/呎
-(在售)</t>
+$2766万
+$31,109/呎
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="C32" s="22" t="inlineStr">
@@ -34990,7 +34982,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -35000,7 +34992,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -35449,12 +35441,12 @@
 (26年-06月-03日)</t>
         </is>
       </c>
-      <c r="H10" s="22" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>G | 186呎 (开放式)
-招标单位
--
-(在售)</t>
+$589万
+$31,656/呎
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">

--- a/九龙-启德-The Henley I/The Henley I_销控明细表.xlsx
+++ b/九龙-启德-The Henley I/The Henley I_销控明细表.xlsx
@@ -30234,7 +30234,7 @@
         </is>
       </c>
       <c r="E478" s="4" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F478" s="3" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>5888000</v>
       </c>
       <c r="I478" s="5" t="n">
-        <v>31656</v>
+        <v>31827</v>
       </c>
       <c r="J478" s="3" t="inlineStr">
         <is>
@@ -30261,7 +30261,7 @@
         <v>5888000</v>
       </c>
       <c r="L478" s="5" t="n">
-        <v>31656</v>
+        <v>31827</v>
       </c>
       <c r="M478" s="3" t="inlineStr">
         <is>
@@ -35443,9 +35443,9 @@
       </c>
       <c r="H10" s="20" t="inlineStr">
         <is>
-          <t>G | 186呎 (开放式)
+          <t>G | 185呎 (开放式)
 $589万
-$31,656/呎
+$31,827/呎
 (26年-09月-15日)</t>
         </is>
       </c>

--- a/九龙-启德-The Henley I/The Henley I_销控明细表.xlsx
+++ b/九龙-启德-The Henley I/The Henley I_销控明细表.xlsx
@@ -17280,34 +17280,34 @@
       </c>
       <c r="F269" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
-        <v>28499000</v>
+        <v>27501500</v>
       </c>
       <c r="I269" s="5" t="n">
-        <v>32057</v>
+        <v>30935</v>
       </c>
       <c r="J269" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K269" s="5" t="n">
-        <v>26332600</v>
+        <v>27501500</v>
       </c>
       <c r="L269" s="5" t="n">
-        <v>29620</v>
+        <v>30935</v>
       </c>
       <c r="M269" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N269" s="3" t="inlineStr">
@@ -30243,7 +30243,7 @@
       </c>
       <c r="G478" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H478" s="5" t="n">
@@ -30537,7 +30537,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -30547,7 +30547,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>226</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -32889,12 +32889,12 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B34" s="22" t="inlineStr">
+      <c r="B34" s="20" t="inlineStr">
         <is>
           <t>A | 889呎 (3房)
-$2850万
-$32,057/呎
-(在售)</t>
+$2750万
+$30,935/呎
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="C34" s="23" t="inlineStr">
@@ -35446,7 +35446,7 @@
           <t>G | 185呎 (开放式)
 $589万
 $31,827/呎
-(26年-09月-15日)</t>
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">

--- a/九龙-启德-The Henley I/The Henley I_销控明细表.xlsx
+++ b/九龙-启德-The Henley I/The Henley I_销控明细表.xlsx
@@ -15602,7 +15602,7 @@
         </is>
       </c>
       <c r="E242" s="4" t="n">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="F242" s="3" t="inlineStr">
         <is>
@@ -15611,14 +15611,14 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
         <v>27658800</v>
       </c>
       <c r="I242" s="5" t="n">
-        <v>31112</v>
+        <v>31077</v>
       </c>
       <c r="J242" s="3" t="inlineStr">
         <is>
@@ -15629,7 +15629,7 @@
         <v>27658800</v>
       </c>
       <c r="L242" s="5" t="n">
-        <v>31112</v>
+        <v>31077</v>
       </c>
       <c r="M242" s="3" t="inlineStr">
         <is>
@@ -32654,10 +32654,10 @@
       </c>
       <c r="B31" s="20" t="inlineStr">
         <is>
-          <t>A | 889呎 (3房)
+          <t>A | 890呎 (3房)
 $2766万
-$31,112/呎
-(26年-09月-16日)</t>
+$31,077/呎
+(26年-10月-12日)</t>
         </is>
       </c>
       <c r="C31" s="22" t="inlineStr">

--- a/九龙-启德-The Henley I/The Henley I_销控明细表.xlsx
+++ b/九龙-启德-The Henley I/The Henley I_销控明细表.xlsx
@@ -16160,7 +16160,7 @@
         </is>
       </c>
       <c r="E251" s="4" t="n">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
@@ -16169,14 +16169,14 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
         <v>27655900</v>
       </c>
       <c r="I251" s="5" t="n">
-        <v>31109</v>
+        <v>31074</v>
       </c>
       <c r="J251" s="3" t="inlineStr">
         <is>
@@ -16187,7 +16187,7 @@
         <v>27655900</v>
       </c>
       <c r="L251" s="5" t="n">
-        <v>31109</v>
+        <v>31074</v>
       </c>
       <c r="M251" s="3" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         </is>
       </c>
       <c r="E269" s="4" t="n">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="F269" s="3" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
         <v>27501500</v>
       </c>
       <c r="I269" s="5" t="n">
-        <v>30935</v>
+        <v>30901</v>
       </c>
       <c r="J269" s="3" t="inlineStr">
         <is>
@@ -17303,7 +17303,7 @@
         <v>27501500</v>
       </c>
       <c r="L269" s="5" t="n">
-        <v>30935</v>
+        <v>30901</v>
       </c>
       <c r="M269" s="3" t="inlineStr">
         <is>
@@ -32733,10 +32733,10 @@
       </c>
       <c r="B32" s="20" t="inlineStr">
         <is>
-          <t>A | 889呎 (3房)
+          <t>A | 890呎 (3房)
 $2766万
-$31,109/呎
-(26年-09月-16日)</t>
+$31,074/呎
+(26年-10月-14日)</t>
         </is>
       </c>
       <c r="C32" s="22" t="inlineStr">
@@ -32891,9 +32891,9 @@
       </c>
       <c r="B34" s="20" t="inlineStr">
         <is>
-          <t>A | 889呎 (3房)
+          <t>A | 890呎 (3房)
 $2750万
-$30,935/呎
+$30,901/呎
 (26年-10月-05日)</t>
         </is>
       </c>

--- a/九龙-启德-The Henley I/The Henley I_销控明细表.xlsx
+++ b/九龙-启德-The Henley I/The Henley I_销控明细表.xlsx
@@ -4384,23 +4384,23 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
-        <v>19833000</v>
+        <v>19138800</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>36060</v>
+        <v>34798</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K61" s="5" t="n">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N61" s="3" t="inlineStr">
@@ -30537,7 +30537,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -30547,7 +30547,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>227</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -31080,12 +31080,12 @@
 (21年-07月-12日)</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 550呎 (2房)
-$1983万
-$36,060/呎
-(在售)</t>
+$1914万
+$34,798/呎
+(26年-10月-23日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
